--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±13分钟</t>
+          <t>07:19采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±12分钟</t>
+          <t>07:19采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±14分钟</t>
+          <t>07:19采样：该车到重点站白桦路明月路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,26 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>07:19采样：该车到重点站沪南路高科西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1066,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1294,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1332,24 +1340,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数159分钟估算，约±6分钟</t>
+          <t>07:19采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1359,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1388,7 +1396,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1408,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1421,24 +1429,24 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1451,34 +1459,34 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数164分钟估算，约±6分钟</t>
+          <t>07:11采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1502,37 +1510,1211 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站康沈路秀康路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>156分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>174分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站浦东大道东波路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>172分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数166分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>162分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数162分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>5/8</t>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,14 +446,14 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -637,29 +637,29 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站白桦路明月路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±15分钟</t>
+          <t>08:21采样：该车到重点站康沈路秀沿路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -999,26 +999,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站沪南路高科西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 49分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1026,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,22 +1046,22 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1075,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1104,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq38，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1149,10 +1145,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1170,7 +1182,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1191,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1314,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1340,24 +1352,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±8分钟</t>
+          <t>08:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1367,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1428,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1459,24 +1471,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:11采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±11分钟</t>
+          <t>08:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1486,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1510,7 +1522,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1535,12 +1547,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1590,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康沈路秀康路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±10分钟</t>
+          <t>08:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1605,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1709,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±10分钟</t>
+          <t>08:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1748,7 +1760,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -1773,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1816,24 +1828,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±12分钟</t>
+          <t>08:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1867,7 +1879,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -1892,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2020,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2046,24 +2058,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站浦东大道东波路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±13分钟</t>
+          <t>08:21采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2073,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2097,7 +2109,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2122,12 +2134,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2165,24 +2177,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数166分钟，约±9分钟</t>
+          <t>07:31采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数152分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2192,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2216,7 +2228,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -2241,12 +2253,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2357,7 +2369,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2395,24 +2407,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数162分钟估算，约±10分钟</t>
+          <t>08:21采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2422,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2446,12 +2458,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2471,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2514,24 +2526,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>183分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±5分钟</t>
+          <t>08:21采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2541,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2570,7 +2582,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2590,12 +2602,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2633,19 +2645,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±8分钟</t>
+          <t>08:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2660,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2689,32 +2701,1571 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>176分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>176.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>168分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>08:11采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>147分钟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>166分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数148分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站浦东大道东波路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数135分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站川周公路康沈路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>9/18</t>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>154分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数154分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -875,29 +875,29 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站康沈路秀沿路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -999,19 +999,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 49分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:51采样，终点ETA 8分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq38，推进10站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1236,27 +1236,31 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1288,33 +1292,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1347,29 +1355,29 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1379,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,12 +1411,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1418,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1466,29 +1474,29 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1498,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,12 +1530,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1537,22 +1545,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1585,29 +1593,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1617,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,12 +1649,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1656,22 +1664,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1709,26 +1717,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,12 +1764,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1775,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1823,29 +1827,29 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>180分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1855,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,12 +1883,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1904,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1941,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1978,10 +1982,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1999,7 +2019,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2058,24 +2078,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±10分钟</t>
+          <t>09:21采样：该车到重点站周东路川周公路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2085,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,12 +2154,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2177,24 +2197,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>07:31采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数152分钟，约±15分钟</t>
+          <t>09:21采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2204,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2228,7 +2248,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -2253,7 +2273,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2286,12 +2306,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2319,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2327,10 +2347,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2348,7 +2384,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2407,24 +2443,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±11分钟</t>
+          <t>09:21采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2434,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2458,7 +2494,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
@@ -2483,12 +2519,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2526,24 +2562,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>183分钟</t>
+          <t>185分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±8分钟</t>
+          <t>09:21采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2553,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,12 +2638,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -2645,24 +2681,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±8分钟</t>
+          <t>09:21采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2672,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2696,7 +2732,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
@@ -2721,12 +2757,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2764,24 +2800,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>176分钟</t>
+          <t>180分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
+          <t>09:21采样：该车到重点站迎春路金松路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2791,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2815,7 +2851,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -2840,7 +2876,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2883,24 +2919,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±12分钟</t>
+          <t>09:21采样：该车到重点站沪南路北中路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2910,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2934,7 +2970,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -2959,12 +2995,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3002,24 +3038,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>182分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±6分钟</t>
+          <t>09:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3029,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3053,7 +3089,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -3078,12 +3114,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3121,24 +3157,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±9分钟</t>
+          <t>09:21采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3148,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3197,12 +3233,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3240,19 +3276,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>177分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数148分钟，约±5分钟</t>
+          <t>09:21采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3267,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,12 +3352,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3359,19 +3395,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站浦东大道东波路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数135分钟，约±5分钟</t>
+          <t>09:21采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3386,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3435,12 +3471,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3478,19 +3514,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站川周公路康沈路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3505,7 +3541,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3554,12 +3590,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3597,19 +3633,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±5分钟</t>
+          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3624,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3653,7 +3689,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3673,12 +3709,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3716,22 +3752,26 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>09:21采样：该车到重点站丁香路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3739,7 +3779,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3763,17 +3803,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3783,13 +3823,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3827,24 +3871,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数154分钟估算，约±10分钟</t>
+          <t>09:21采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3854,7 +3898,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3883,7 +3927,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3903,12 +3947,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3946,19 +3990,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
+          <t>09:21采样：该车到重点站金杨路金业路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3973,7 +4017,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4002,7 +4046,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4022,12 +4066,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4065,24 +4109,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±14分钟</t>
+          <t>09:21采样：该车到重点站康沈路秀康路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4092,7 +4136,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4121,7 +4165,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4141,12 +4185,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4184,24 +4228,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±8分钟</t>
+          <t>09:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4211,7 +4255,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4240,32 +4284,857 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>09:21采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>142.0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1712,27 +1712,31 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1740,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1764,12 +1768,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1794,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1827,31 +1831,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>180分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:51采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2078,24 +2078,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站周东路川周公路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±8分钟</t>
+          <t>同车下一次反向发车10:15，减去该车自身同类时段历史终点停站中位数25分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2192,29 +2192,29 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>175分钟</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2263,22 +2263,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,29 +2438,29 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2509,22 +2509,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2557,29 +2557,29 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>185分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2628,22 +2628,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2681,24 +2681,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±15分钟</t>
+          <t>同车下一次反向发车10:45，减去该车自身同类时段历史终点停站中位数18分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2747,22 +2747,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2800,26 +2800,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>180分钟</t>
+          <t>181分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站迎春路金松路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:11采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2827,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,12 +2847,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2866,22 +2862,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2919,26 +2915,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路北中路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:11采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2946,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2975,7 +2967,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2985,22 +2977,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3038,24 +3030,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>182分钟</t>
+          <t>181分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±13分钟</t>
+          <t>10:21采样：该车到重点站长岛路张杨北路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3065,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,7 +3081,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -3114,12 +3106,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3152,29 +3144,29 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3184,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3208,12 +3200,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3233,12 +3225,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3276,19 +3268,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>177分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站长岛路张杨北路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3303,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3352,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3395,19 +3387,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站周东路川周公路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3422,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3471,12 +3463,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3514,19 +3506,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3541,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3590,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3633,19 +3625,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3660,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3709,12 +3701,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3756,7 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站丁香路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3779,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3833,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3871,24 +3863,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±7分钟</t>
+          <t>10:21采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3898,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3947,12 +3939,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3990,19 +3982,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站金杨路金业路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -4017,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4066,12 +4058,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4109,24 +4101,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站康沈路秀康路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±15分钟</t>
+          <t>10:21采样：该车到重点站锦绣路罗山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4136,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,7 +4152,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
@@ -4185,7 +4177,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4228,19 +4220,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±7分钟</t>
+          <t>10:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4255,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4304,12 +4296,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4347,24 +4339,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±9分钟</t>
+          <t>10:21采样：该车到重点站迎春路金松路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4374,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4423,12 +4415,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4577,24 +4569,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±13分钟</t>
+          <t>10:21采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4604,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,12 +4620,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4653,12 +4645,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4696,19 +4688,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+          <t>10:21采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -4723,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4752,7 +4744,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4772,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4815,24 +4807,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±6分钟</t>
+          <t>10:21采样：该车到重点站沪南路华夏西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4842,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4871,7 +4863,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4891,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4934,24 +4926,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>10:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4961,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,7 +4982,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -5010,12 +5002,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5053,24 +5045,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>10:21采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5080,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5109,32 +5101,984 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站博兴路兰城路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站关岳路康达路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>138.5</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>3/28</t>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>131分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数131分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>155.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2800,19 +2800,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>181分钟</t>
+          <t>180分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:11采样，终点ETA 32分钟</t>
+          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 11分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站长岛路张杨北路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3096,22 +3096,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3149,24 +3149,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3263,24 +3263,24 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站长岛路张杨北路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3399,14 +3399,10 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站周东路川周公路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3414,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,7 +3439,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3468,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3506,19 +3502,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>10:51采样：该车到重点站东葛路东靖路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数8分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3533,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,22 +3568,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3616,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3630,14 +3626,14 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3652,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,12 +3672,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3701,12 +3697,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3739,29 +3735,29 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3771,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,12 +3791,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3810,22 +3806,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3858,24 +3854,24 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3890,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,12 +3910,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3929,22 +3925,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3977,24 +3973,24 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -4009,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,12 +4029,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4058,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4106,14 +4102,14 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站锦绣路罗山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>11:01采样：该车到重点站东波路莱阳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数14分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4128,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4177,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4215,29 +4211,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4247,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,12 +4267,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4286,22 +4282,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4339,26 +4335,22 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站迎春路金松路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4366,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,7 +4387,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4405,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4440,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq56，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4481,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4489,10 +4481,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4510,7 +4518,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4569,26 +4577,22 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 18分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4596,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,7 +4629,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4645,12 +4649,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4683,29 +4687,29 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4715,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,12 +4743,12 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4764,12 +4768,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4807,19 +4811,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站沪南路华夏西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
+          <t>11:11采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4834,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4887,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4926,24 +4930,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±7分钟</t>
+          <t>同车下一次反向发车12:15，减去该车自身同类时段历史终点停站中位数24分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4953,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,7 +4986,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4992,22 +4996,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5049,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -5057,12 +5061,12 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±7分钟</t>
+          <t>11:21采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5072,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5126,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5164,24 +5168,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站博兴路兰城路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+          <t>11:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5191,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5244,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5283,24 +5287,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站关岳路康达路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±14分钟</t>
+          <t>11:21采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5310,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,7 +5363,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5402,24 +5406,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±10分钟</t>
+          <t>11:21采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5429,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5482,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5533,12 +5537,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+          <t>11:21采样：该车到重点站锦绣路花木路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5548,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5577,7 +5581,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5640,19 +5644,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数131分钟估算，约±10分钟</t>
+          <t>11:21采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5667,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5696,7 +5700,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5716,12 +5720,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5729,24 +5733,24 @@
       <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5759,34 +5763,34 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±8分钟</t>
+          <t>11:21采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5800,12 +5804,12 @@
       <c r="T45" s="2" t="inlineStr"/>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>计划发车</t>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5815,7 +5819,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5835,12 +5839,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5848,24 +5852,24 @@
       <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5878,34 +5882,34 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>11:21采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5919,12 +5923,12 @@
       <c r="T46" s="2" t="inlineStr"/>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5934,7 +5938,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5954,12 +5958,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6013,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±8分钟</t>
+          <t>11:21采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -6024,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6053,32 +6057,976 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>11:21采样：该车到重点站白桦路明月路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>11:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>11:21采样：该车到重点站浦东大道东波路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="Y53" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr">
-        <is>
-          <t>134.5</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>1/28</t>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>139.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>142.7</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,22 +1545,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,18 +2029,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,22 +2148,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2273,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2394,18 +2398,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2519,12 +2527,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2638,12 +2646,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2747,22 +2755,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2872,12 +2880,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2987,12 +2995,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,12 +3114,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3225,12 +3233,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3357,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3578,12 +3586,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3811,17 +3819,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3930,17 +3938,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4251,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4297,7 +4305,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,12 +4415,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4453,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq56，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq61，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4473,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4539,7 +4547,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4572,27 +4580,31 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 18分钟</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4600,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,12 +4636,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4649,12 +4661,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4692,12 +4704,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -4719,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4768,12 +4780,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4877,22 +4889,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4925,29 +4937,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车12:15，减去该车自身同类时段历史终点停站中位数24分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4957,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,12 +4993,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -5006,12 +5018,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5044,29 +5056,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5076,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,12 +5112,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5125,12 +5137,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5163,29 +5175,29 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5195,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,12 +5231,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5244,12 +5256,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5282,29 +5294,29 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5314,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5338,12 +5350,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5353,22 +5365,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5401,29 +5413,29 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5433,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,12 +5469,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5482,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5520,29 +5532,29 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站锦绣路花木路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5552,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5576,12 +5588,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5601,12 +5613,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5639,29 +5651,29 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5671,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,12 +5707,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5720,12 +5732,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5763,19 +5775,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
+          <t>12:21采样：该车到重点站康沈路秀沿路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -5790,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5839,12 +5851,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5882,26 +5894,22 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站沪南路华夏西路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5909,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5933,12 +5941,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5948,22 +5956,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6001,24 +6009,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
+          <t>12:21采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6028,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,7 +6060,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
@@ -6077,12 +6085,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6120,24 +6128,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站白桦路明月路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±15分钟</t>
+          <t>12:21采样：该车到重点站沪南路北中路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6147,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6196,12 +6204,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6239,24 +6247,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
+          <t>12:21采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6266,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6290,7 +6298,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
@@ -6315,12 +6323,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6358,19 +6366,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站浦东大道东波路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±7分钟</t>
+          <t>12:21采样：该车到重点站浦建路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6385,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6434,12 +6442,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6477,22 +6485,26 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>12:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6500,7 +6512,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,17 +6536,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6544,17 +6556,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6592,22 +6604,26 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>12:21采样：该车到重点站浦建路锦绣路 ETA 35分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6615,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,17 +6655,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6659,17 +6675,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6723,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -6719,12 +6735,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±8分钟</t>
+          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6734,7 +6750,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6763,7 +6779,7 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6788,7 +6804,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6826,19 +6842,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±15分钟</t>
+          <t>12:21采样：该车到重点站金杨路金业路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6853,7 +6869,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,7 +6898,7 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6902,12 +6918,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6945,19 +6961,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±13分钟</t>
+          <t>12:21采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6972,7 +6988,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,32 +7017,738 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="Y56" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z55" s="2" t="inlineStr">
+      <c r="Z56" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
+      <c r="AA56" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>142.7</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>12/28</t>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>139.3</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2636,22 +2636,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3104,22 +3104,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3223,17 +3223,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3814,22 +3814,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4290,22 +4290,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4410,17 +4410,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5418,24 +5418,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5537,24 +5537,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5722,22 +5722,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5770,24 +5770,24 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站康沈路秀沿路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5889,27 +5889,31 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5917,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,12 +5945,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5966,12 +5970,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6004,12 +6008,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -6021,12 +6025,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6036,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,12 +6064,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6090,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6123,29 +6127,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路北中路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±13分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6155,7 +6159,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,12 +6183,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6194,22 +6198,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6242,29 +6246,29 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±11分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6274,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,12 +6302,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6313,17 +6317,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6361,29 +6365,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站浦建路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6393,7 +6397,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6417,12 +6421,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6442,12 +6446,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6485,26 +6489,22 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6604,26 +6604,22 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站浦建路锦绣路 ETA 35分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 45分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6631,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6660,7 +6656,7 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6680,7 +6676,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6735,12 +6731,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±10分钟</t>
+          <t>13:21采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6750,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6789,22 +6785,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6842,26 +6838,22 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金业路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 47分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6869,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6893,17 +6885,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6913,17 +6905,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6973,12 +6965,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±13分钟</t>
+          <t>13:21采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6988,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7161,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7310,24 +7302,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±5分钟</t>
+          <t>13:21采样：该车到重点站锦绣路花木路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7337,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,7 +7358,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7386,7 +7378,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7429,24 +7421,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±7分钟</t>
+          <t>13:21采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7456,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7485,7 +7477,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7505,7 +7497,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7548,24 +7540,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±7分钟</t>
+          <t>13:21采样：该车到重点站康沈路秀康路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7575,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7599,12 +7591,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7624,7 +7616,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7672,14 +7664,14 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±12分钟</t>
+          <t>13:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7694,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,30 +7715,740 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y61" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z61" s="2" t="inlineStr">
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>139.7</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>135.3</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>133分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>148.7</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
         <is>
           <t>9/29</t>
         </is>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2641,17 +2641,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4052,17 +4052,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4410,17 +4410,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5008,22 +5008,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5727,17 +5727,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6484,27 +6484,31 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6512,7 +6516,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,12 +6540,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6561,12 +6565,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6599,27 +6603,31 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 45分钟</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6627,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,12 +6659,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6676,12 +6684,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6714,29 +6722,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6746,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,12 +6778,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6795,7 +6803,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6833,27 +6841,31 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 47分钟</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6861,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,17 +6897,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6905,17 +6917,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6948,29 +6960,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6980,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,12 +7016,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7019,22 +7031,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7181,12 +7193,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7214,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7222,10 +7234,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7243,7 +7271,7 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7302,24 +7330,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站锦绣路花木路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±9分钟</t>
+          <t>13:51采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7329,7 +7357,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,7 +7406,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7421,19 +7449,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±8分钟</t>
+          <t>13:51采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7448,7 +7476,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,12 +7525,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7540,24 +7568,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站康沈路秀康路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±11分钟</t>
+          <t>13:51采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7567,7 +7595,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7591,7 +7619,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
@@ -7616,12 +7644,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7659,19 +7687,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±12分钟</t>
+          <t>13:51采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7686,7 +7714,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7735,12 +7763,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7778,22 +7806,26 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>13:31采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数152分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7801,7 +7833,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7825,17 +7857,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7845,17 +7877,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7893,19 +7925,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>13:51采样：该车到重点站浦东大道东波路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7920,7 +7952,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7949,7 +7981,7 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7969,7 +8001,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8039,7 +8071,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8158,7 +8190,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,12 +8239,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8309,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8396,7 +8428,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8445,12 +8477,250 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
           <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>152.7</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4770,22 +4770,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5246,22 +5246,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>152.7</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6846,24 +6846,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq53，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7325,29 +7325,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>13:51采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7396,17 +7396,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7449,26 +7449,22 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>13:51采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:21采样，终点ETA 45分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7476,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7500,12 +7496,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7525,12 +7521,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7568,24 +7564,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>13:51采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±10分钟</t>
+          <t>14:21采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7595,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7644,12 +7640,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7687,24 +7683,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>13:51采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±12分钟</t>
+          <t>14:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7714,7 +7710,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7738,7 +7734,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
@@ -7763,12 +7759,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7806,24 +7802,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>13:31采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数152分钟，约±9分钟</t>
+          <t>14:21采样：该车到重点站云山路碧云路 ETA 42分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7833,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7857,7 +7853,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
@@ -7882,7 +7878,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>152.7</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7930,19 +7926,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>13:51采样：该车到重点站浦东大道东波路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+          <t>14:21采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7952,7 +7948,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8001,12 +7997,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8049,19 +8045,19 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数133分钟估算，约±9分钟</t>
+          <t>14:21采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8071,7 +8067,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8095,12 +8091,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8120,12 +8116,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8163,19 +8159,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+          <t>14:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8190,7 +8186,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8219,7 +8215,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8239,7 +8235,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8287,14 +8283,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>14:21采样：该车到重点站康丽路康恩路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -8309,7 +8305,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8338,7 +8334,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8358,12 +8354,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8547,7 +8543,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8666,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8715,12 +8711,369 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>123分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数123分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3342,14 +3342,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>169.0</t>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5484,22 +5484,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq53，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq61，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7292,7 +7292,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7444,27 +7444,31 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:21采样，终点ETA 45分钟</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7472,7 +7476,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7496,12 +7500,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7521,12 +7525,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7563,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -7576,12 +7580,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7591,7 +7595,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7615,12 +7619,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7645,7 +7649,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7678,29 +7682,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7710,7 +7714,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7734,12 +7738,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7759,12 +7763,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7797,29 +7801,29 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站云山路碧云路 ETA 42分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7829,7 +7833,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7853,12 +7857,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7878,12 +7882,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7916,29 +7920,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7948,7 +7952,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7972,12 +7976,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7997,12 +8001,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8039,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -8052,12 +8056,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8067,7 +8071,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8091,12 +8095,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8121,7 +8125,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8159,24 +8163,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±6分钟</t>
+          <t>15:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8186,7 +8190,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8235,12 +8239,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8278,19 +8282,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站康丽路康恩路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+          <t>15:21采样：该车到重点站锦绣路花木路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -8305,7 +8309,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8354,12 +8358,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8397,19 +8401,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±5分钟</t>
+          <t>15:21采样：该车到重点站丁香路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -8424,7 +8428,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8453,7 +8457,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8473,12 +8477,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8516,24 +8520,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±12分钟</t>
+          <t>15:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8543,7 +8547,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8572,7 +8576,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8592,12 +8596,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8635,24 +8639,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>15:21采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8662,7 +8666,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8691,7 +8695,7 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8711,12 +8715,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8754,24 +8758,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+          <t>15:21采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8781,7 +8785,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8805,12 +8809,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8830,12 +8834,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8904,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8949,12 +8953,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8962,24 +8966,24 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8992,34 +8996,30 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9043,37 +9043,497 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>21/29</t>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>149.7</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,14 +1307,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,22 +1783,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>150.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,17 +2398,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2870,22 +2870,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3347,17 +3347,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3695,22 +3695,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3933,22 +3933,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4405,22 +4405,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5127,22 +5127,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>150.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5841,22 +5841,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6674,22 +6674,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6912,22 +6912,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7806,24 +7806,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7925,24 +7925,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8044,24 +8044,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8158,29 +8158,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8277,29 +8277,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站锦绣路花木路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8358,12 +8358,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8396,29 +8396,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站丁香路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8520,26 +8520,22 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 36分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8547,7 +8543,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8576,7 +8572,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8596,7 +8592,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8639,7 +8635,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -8651,12 +8647,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±7分钟</t>
+          <t>16:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8666,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8720,7 +8716,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8758,24 +8754,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±13分钟</t>
+          <t>16:21采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8785,7 +8781,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8809,7 +8805,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
@@ -8834,12 +8830,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8877,24 +8873,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数123分钟估算，约±5分钟</t>
+          <t>16:21采样：该车到重点站迎春路长柳路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8904,7 +8900,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8933,7 +8929,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8953,7 +8949,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9019,7 +9015,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9107,19 +9103,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±11分钟</t>
+          <t>16:21采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -9134,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9163,7 +9159,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9183,7 +9179,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9226,22 +9222,26 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>16:21采样：该车到重点站浦建路锦绣路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9273,17 +9273,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9341,19 +9341,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±14分钟</t>
+          <t>16:21采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>150.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9430,24 +9430,24 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9460,30 +9460,34 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>16:21采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9497,43 +9501,1098 @@
       <c r="T76" s="2" t="inlineStr"/>
       <c r="U76" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>158.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
           <t>16:08</t>
         </is>
       </c>
-      <c r="V76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W76" s="2" t="inlineStr">
+      <c r="W77" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X76" s="2" t="inlineStr">
+      <c r="X77" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y76" s="2" t="inlineStr">
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z76" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr"/>
-      <c r="AC76" s="2" t="inlineStr">
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
         <is>
           <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>16:21采样：该车到重点站浦东大道东波路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>16:21采样：该车到重点站沪南路华夏西路 ETA 34分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>140.2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,22 +1545,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>150.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2517,17 +2517,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2755,22 +2755,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4052,22 +4052,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4176,17 +4176,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4770,22 +4770,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4889,22 +4889,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>150.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5365,22 +5365,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5960,22 +5960,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6317,22 +6317,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7150,22 +7150,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7515,22 +7515,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7753,22 +7753,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7991,22 +7991,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8348,22 +8348,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8413,12 +8413,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8515,27 +8515,31 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 36分钟</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8543,7 +8547,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8567,12 +8571,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8582,22 +8586,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8630,29 +8634,29 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8662,7 +8666,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8686,12 +8690,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8711,7 +8715,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8754,26 +8758,22 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8820,22 +8820,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8868,29 +8868,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站迎春路长柳路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9098,29 +9098,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9154,12 +9154,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>150.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9217,29 +9217,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站浦建路锦绣路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9341,24 +9341,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±14分钟</t>
+          <t>17:21采样：该车到重点站锦绣路罗山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9460,19 +9460,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±13分钟</t>
+          <t>17:21采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9690,24 +9690,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站浦东大道东波路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±9分钟</t>
+          <t>17:21采样：该车到重点站浦建路锦绣路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9809,24 +9809,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站沪南路华夏西路 ETA 34分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±15分钟</t>
+          <t>17:21采样：该车到重点站迎春路金松路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9928,22 +9928,26 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>17:21采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9951,7 +9955,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9975,17 +9979,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9995,17 +9999,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10043,22 +10047,26 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>17:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10066,7 +10074,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10090,17 +10098,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10110,17 +10118,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10158,19 +10166,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±12分钟</t>
+          <t>17:21采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10185,7 +10193,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10214,7 +10222,7 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10234,7 +10242,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10300,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10354,7 +10362,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10392,24 +10400,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±7分钟</t>
+          <t>17:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10419,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10448,7 +10456,7 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10468,12 +10476,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10511,24 +10519,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±14分钟</t>
+          <t>17:21采样：该车到重点站川周公路康沈路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10538,7 +10546,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10567,32 +10575,980 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>142.2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>143分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站关岳路康达路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数134分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>140.2</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>157分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站浦东大道东波路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y85" s="2" t="inlineStr">
+      <c r="Y88" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z85" s="2" t="inlineStr">
+      <c r="Z88" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
+      <c r="AA88" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB85" s="2" t="inlineStr">
-        <is>
-          <t>140.2</t>
-        </is>
-      </c>
-      <c r="AC85" s="2" t="inlineStr">
-        <is>
-          <t>12/30</t>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>145.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>151分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数151分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>147分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数147分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,22 +2029,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,22 +2985,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3695,22 +3695,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4171,22 +4171,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5246,22 +5246,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6079,22 +6079,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7396,22 +7396,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8358,12 +8358,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8868,31 +8868,27 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:51采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8900,7 +8896,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8924,12 +8920,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8939,22 +8935,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9061,7 @@
       <c r="AB72" s="2" t="inlineStr"/>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9103,24 +9099,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9130,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9169,22 +9165,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9222,24 +9218,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9249,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9288,22 +9284,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9336,29 +9332,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站锦绣路罗山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9368,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9392,12 +9388,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9417,12 +9413,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9451,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9465,19 +9461,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9487,7 +9483,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9511,12 +9507,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9526,22 +9522,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9648,7 @@
       <c r="AB77" s="2" t="inlineStr"/>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9690,26 +9686,22 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站浦建路锦绣路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9717,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9741,12 +9733,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9766,12 +9758,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -9804,29 +9796,29 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站迎春路金松路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9836,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9860,12 +9852,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9885,12 +9877,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9928,19 +9920,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站康沈路秀沿路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9955,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9994,22 +9986,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10047,19 +10039,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站长岛路张杨北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10074,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10123,12 +10115,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -10166,24 +10158,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±12分钟</t>
+          <t>18:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10193,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10217,7 +10209,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
@@ -10242,12 +10234,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10362,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10400,19 +10392,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±8分钟</t>
+          <t>18:21采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10427,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10476,12 +10468,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10519,24 +10511,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站川周公路康沈路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±15分钟</t>
+          <t>18:21采样：该车到重点站锦绣路罗山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10546,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10570,7 +10562,7 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
@@ -10595,12 +10587,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -10638,24 +10630,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站关岳路康达路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数134分钟，约±12分钟</t>
+          <t>18:21采样：该车到重点站迎春路金松路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10665,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10714,12 +10706,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10757,19 +10749,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站浦东大道东波路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站丁香路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10784,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10833,12 +10825,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10881,19 +10873,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±6分钟</t>
+          <t>18:21采样：该车到重点站锦绣路花木路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10903,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10932,7 +10924,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10952,12 +10944,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10995,19 +10987,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11022,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11051,7 +11043,7 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11071,12 +11063,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11114,24 +11106,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11141,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11170,7 +11162,7 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11190,12 +11182,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11310,7 +11302,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -11348,19 +11340,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数151分钟估算，约±6分钟</t>
+          <t>18:21采样：该车到重点站康沈路秀康路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11375,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11404,7 +11396,7 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11424,12 +11416,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -11472,19 +11464,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数147分钟估算，约±12分钟</t>
+          <t>18:21采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11494,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11523,32 +11515,849 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>144.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>15/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>143分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>18:21采样：该车到重点站川周公路康沈路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>18:21采样：该车到重点站博兴路兰城路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>13/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y93" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z93" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>151.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>160.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>27/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
+      <c r="AA99" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>17/30</t>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>149.8</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>11/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>144.2</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,22 +1783,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>155.7</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,22 +2398,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2870,22 +2870,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3576,17 +3576,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3933,22 +3933,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>146.3</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4176,17 +4176,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4651,22 +4651,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>144.2</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5127,22 +5127,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5484,22 +5484,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>155.7</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5841,22 +5841,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6436,17 +6436,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6674,22 +6674,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>146.3</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8591,17 +8591,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>144.2</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8945,12 +8945,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9337,19 +9337,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9403,22 +9403,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>155.7</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9527,17 +9527,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -9681,27 +9681,31 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 20分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9709,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9733,12 +9737,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9748,22 +9752,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -9801,24 +9805,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9828,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9867,22 +9871,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9915,29 +9919,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站康沈路秀沿路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9947,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9971,12 +9975,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9991,17 +9995,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -10034,24 +10038,24 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站长岛路张杨北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10066,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10090,12 +10094,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10105,17 +10109,17 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10153,29 +10157,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10185,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10209,12 +10213,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10224,22 +10228,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>146.3</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10272,27 +10276,31 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10300,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10324,37 +10332,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10387,29 +10395,29 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10419,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10443,12 +10451,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10458,22 +10466,22 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10506,29 +10514,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站锦绣路罗山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10538,7 +10546,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10562,12 +10570,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10587,12 +10595,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10630,26 +10638,22 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站迎春路金松路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10657,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10686,7 +10690,7 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10706,12 +10710,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10749,26 +10753,22 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站丁香路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10800,12 +10800,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10880,12 +10880,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站锦绣路花木路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±10分钟</t>
+          <t>19:21采样：该车到重点站长岛路张杨北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10999,7 +10999,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站康沈路秀沿路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11106,24 +11106,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±7分钟</t>
+          <t>19:21采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11182,12 +11182,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11225,22 +11225,26 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>19:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11248,7 +11252,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11272,17 +11276,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11292,17 +11296,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -11345,14 +11349,14 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站康沈路秀康路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±6分钟</t>
+          <t>19:21采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11367,7 +11371,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11416,12 +11420,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11459,24 +11463,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±13分钟</t>
+          <t>19:21采样：该车到重点站浦建路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11486,7 +11490,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11510,7 +11514,7 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
@@ -11535,12 +11539,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>144.2</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -11578,19 +11582,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站川周公路康沈路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站锦绣路罗山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -11605,7 +11609,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11654,12 +11658,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -11697,19 +11701,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站博兴路兰城路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±15分钟</t>
+          <t>19:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -11724,7 +11728,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11773,7 +11777,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11816,24 +11820,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±10分钟</t>
+          <t>19:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11843,7 +11847,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11872,7 +11876,7 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11892,12 +11896,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -11935,22 +11939,26 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>19:21采样：该车到重点站白桦路明月路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -11958,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11982,17 +11990,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12002,13 +12010,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB97" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -12046,22 +12058,26 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>19:21采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12069,7 +12085,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12093,17 +12109,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12113,17 +12129,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -12166,19 +12182,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±14分钟</t>
+          <t>19:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12188,7 +12204,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12217,7 +12233,7 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12237,12 +12253,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -12250,24 +12266,24 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12280,30 +12296,34 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>19:21采样：该车到重点站博兴路兰城路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12317,47 +12337,872 @@
       <c r="T100" s="2" t="inlineStr"/>
       <c r="U100" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>19:21采样：该车到重点站川周公路康沈路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W100" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>9/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>19:21采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>147.8</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>1/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="X104" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="Y104" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z100" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA100" s="2" t="inlineStr">
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB100" s="2" t="inlineStr">
-        <is>
-          <t>140.7</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>11/31</t>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>146.7</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>21/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>17/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>4/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC107"/>
+  <dimension ref="A1:AC110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2517,22 +2517,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,22 +2985,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3104,22 +3104,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4656,17 +4656,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5603,22 +5603,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6079,22 +6079,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8110,22 +8110,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8358,12 +8358,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8945,12 +8945,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10352,17 +10352,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10633,27 +10633,31 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10661,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10685,12 +10689,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10710,12 +10714,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10748,27 +10752,31 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10776,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10800,12 +10808,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10825,12 +10833,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10863,12 +10871,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -10880,12 +10888,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站长岛路张杨北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10895,7 +10903,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10919,12 +10927,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10949,7 +10957,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10982,24 +10990,24 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站康沈路秀沿路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11014,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11038,12 +11046,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11053,22 +11061,22 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -11101,29 +11109,29 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11133,7 +11141,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11157,12 +11165,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11182,12 +11190,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11220,29 +11228,29 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11252,7 +11260,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11276,12 +11284,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11301,12 +11309,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11339,29 +11347,29 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11371,7 +11379,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11395,12 +11403,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11420,7 +11428,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11458,29 +11466,29 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站浦建路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11490,7 +11498,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11514,12 +11522,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11539,12 +11547,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11582,19 +11590,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站锦绣路罗山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>19:31采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -11609,7 +11617,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11658,12 +11666,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -11701,26 +11709,22 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11728,7 +11732,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11752,12 +11756,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11767,22 +11771,22 @@
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -11820,26 +11824,22 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11939,19 +11939,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站白桦路明月路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±5分钟</t>
+          <t>20:21采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12015,12 +12015,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -12058,24 +12058,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±14分钟</t>
+          <t>20:21采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12177,24 +12177,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±13分钟</t>
+          <t>20:21采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12296,19 +12296,19 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站博兴路兰城路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+          <t>20:02采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12372,12 +12372,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -12427,12 +12427,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站川周公路康沈路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±15分钟</t>
+          <t>20:21采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -12534,19 +12534,19 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+          <t>20:21采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12610,12 +12610,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -12653,24 +12653,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±6分钟</t>
+          <t>20:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -12887,22 +12887,26 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>20:21采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12910,7 +12914,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12934,17 +12938,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12954,17 +12958,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -13002,24 +13006,24 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>20:21采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -13029,7 +13033,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13058,7 +13062,7 @@
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
@@ -13078,12 +13082,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -13091,24 +13095,24 @@
       <c r="A107" s="2" t="inlineStr"/>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -13126,29 +13130,29 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+          <t>20:21采样：该车到重点站白桦路明月路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13162,47 +13166,404 @@
       <c r="T107" s="2" t="inlineStr"/>
       <c r="U107" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>146.2</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>20:21采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr">
+      <c r="W108" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X107" s="2" t="inlineStr">
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>5/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y107" s="2" t="inlineStr">
+      <c r="Y109" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z107" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA107" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB107" s="2" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="AC107" s="2" t="inlineStr">
-        <is>
-          <t>4/31</t>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>140.8</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>14/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>134.8</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>3/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -989,29 +989,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:51采样，终点ETA 8分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1046,17 +1046,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1826,29 +1826,29 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:51采样，终点ETA 8分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,17 +1883,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2072,36 +2072,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车10:15，减去该车自身同类时段历史终点停站中位数25分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2133,17 +2129,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2153,17 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2272,17 +2268,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2403,17 +2399,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2522,17 +2518,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2679,36 +2675,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车10:45，减去该车自身同类时段历史终点停站中位数18分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -2740,17 +2732,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2760,17 +2752,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -2798,29 +2790,29 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>180分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 11分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
@@ -2831,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2847,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2875,17 +2867,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2913,29 +2905,29 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:11采样，终点ETA 8分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
@@ -2946,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,17 +2962,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2990,17 +2982,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3109,17 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3352,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3385,29 +3377,29 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 9分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
@@ -3442,17 +3434,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3462,12 +3454,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3500,36 +3492,32 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10:51采样：该车到重点站东葛路东靖路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数8分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3537,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3549,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3581,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3700,17 +3688,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4095,36 +4083,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11:01采样：该车到重点站东波路莱阳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数14分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4132,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4140,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4176,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4295,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -4333,29 +4317,29 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 13分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
@@ -4390,17 +4374,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4410,12 +4394,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4612,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4656,17 +4640,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4775,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4813,36 +4797,32 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:11采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4874,17 +4854,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4894,17 +4874,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5132,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5251,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5370,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5489,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5608,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5735,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5780,7 +5760,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -5802,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,7 +5801,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5846,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5965,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6084,17 +6064,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6203,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6441,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -6798,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6897,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7074,36 +7054,32 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7135,17 +7111,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7155,17 +7131,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7401,17 +7377,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7520,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7639,17 +7615,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7758,17 +7734,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8006,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8115,17 +8091,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8329,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8472,17 +8448,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -8748,29 +8724,29 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 7分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
@@ -8805,17 +8781,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8825,17 +8801,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8863,29 +8839,29 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:51采样，终点ETA 6分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
@@ -8920,17 +8896,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8940,17 +8916,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -8978,12 +8954,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -9040,7 +9016,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9126,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9170,17 +9146,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9294,12 +9270,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9408,17 +9384,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9527,17 +9503,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9565,12 +9541,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -9598,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9627,7 +9603,7 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9713,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9757,17 +9733,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9876,17 +9852,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9995,17 +9971,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10114,17 +10090,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10219,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10352,17 +10328,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10471,17 +10447,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10590,12 +10566,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10709,17 +10685,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -10828,12 +10804,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10947,17 +10923,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -11022,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11066,17 +11042,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11185,17 +11161,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11290,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11409,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11542,17 +11518,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -11580,36 +11556,32 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11641,17 +11613,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11661,17 +11633,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -11704,27 +11676,31 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11732,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11756,12 +11732,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11776,17 +11752,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -11819,27 +11795,31 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11847,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11871,12 +11851,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11896,12 +11876,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -11929,36 +11909,32 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -11966,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11990,17 +11966,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12010,17 +11986,13 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB97" s="2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr"/>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -12048,36 +12020,32 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12085,7 +12053,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12109,17 +12077,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12129,17 +12097,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -12167,36 +12135,32 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12204,7 +12168,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12228,17 +12192,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12248,17 +12212,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -12286,36 +12250,32 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>20:02采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12323,7 +12283,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12331,10 +12291,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12347,17 +12323,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12367,17 +12343,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -12405,36 +12381,32 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12442,7 +12414,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12466,17 +12438,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12486,17 +12458,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -12524,36 +12496,32 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12561,7 +12529,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12585,17 +12553,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12605,17 +12573,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -12643,36 +12611,32 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -12680,7 +12644,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12704,17 +12668,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12724,17 +12688,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -12762,12 +12726,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -12824,7 +12788,7 @@
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12849,7 +12813,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -12877,36 +12841,32 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12914,7 +12874,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12938,17 +12898,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12958,17 +12918,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -12996,36 +12956,32 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -13033,7 +12989,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13057,17 +13013,17 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
@@ -13077,17 +13033,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -13115,36 +13071,32 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>22:14</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站白桦路明月路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -13152,7 +13104,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13176,17 +13128,17 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr">
@@ -13196,17 +13148,17 @@
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -13234,36 +13186,32 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>22:14</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
       <c r="N108" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -13271,7 +13219,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13295,17 +13243,17 @@
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
@@ -13315,17 +13263,17 @@
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -13353,36 +13301,32 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -13390,7 +13334,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13414,17 +13358,17 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z109" s="2" t="inlineStr">
@@ -13434,17 +13378,17 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13472,36 +13416,32 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -13509,7 +13449,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13533,17 +13473,17 @@
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X110" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z110" s="2" t="inlineStr">
@@ -13553,17 +13493,17 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-浦东35路.xlsx
+++ b/data/export/2026-09-23-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2867,17 +2867,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9852,17 +9852,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9971,17 +9971,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12020,32 +12020,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12053,7 +12057,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12077,17 +12081,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12097,12 +12101,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12168,7 +12172,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12255,7 +12259,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12283,7 +12287,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12381,32 +12385,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12414,7 +12422,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12438,17 +12446,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12458,17 +12466,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -12496,32 +12504,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12529,7 +12541,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12553,17 +12565,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12573,17 +12585,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -12644,7 +12656,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12726,12 +12738,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -12759,7 +12771,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12767,10 +12779,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q104" s="2" t="inlineStr"/>
-      <c r="R104" s="2" t="inlineStr"/>
-      <c r="S104" s="2" t="inlineStr"/>
-      <c r="T104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12874,7 +12902,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12928,7 +12956,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -12956,32 +12984,36 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12989,7 +13021,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13013,17 +13045,17 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
@@ -13033,17 +13065,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13136,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13158,7 +13190,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -13219,7 +13251,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13273,7 +13305,7 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13366,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13388,7 +13420,7 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -13449,7 +13481,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
